--- a/data/trans_orig/IP1015-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Estudios-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84034</t>
+          <t>83357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174192</t>
+          <t>174563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473053</t>
+          <t>473601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>889807</t>
+          <t>890266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154319</t>
+          <t>154758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328539</t>
+          <t>328837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>716400</t>
+          <t>716411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721302</t>
+          <t>721300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1397462</t>
+          <t>1397380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1402324</t>
+          <t>1402322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447286</t>
+          <t>446789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486671</t>
+          <t>486354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936034</t>
+          <t>935465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941415</t>
+          <t>941418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>704759</t>
+          <t>704531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741412</t>
+          <t>741935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746893</t>
+          <t>746891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1448300</t>
+          <t>1448251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485131</t>
+          <t>485137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>957428</t>
+          <t>957410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184272</t>
+          <t>184241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356952</t>
+          <t>356387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>740621</t>
+          <t>740067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1444446</t>
+          <t>1445035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1015-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3531</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3488</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3527</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3149</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83314</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86145</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83357</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174563</t>
+          <t>174185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3390</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>476291</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>472383</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>476291</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>473601</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890266</t>
+          <t>889569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3383</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3677</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157465</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154755</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157465</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154758</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328837</t>
+          <t>328528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,92 +1751,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>674</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5563</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>719900</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>716404</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>721301</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>719900</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>716411</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721300</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1397380</t>
+          <t>1397446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1402322</t>
+          <t>1402321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2438,47 +2438,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2911</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6050</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>490363</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>486641</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>491798</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>449220</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>446789</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>447291</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>490363</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>486354</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>491798</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1352</t>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935465</t>
+          <t>935774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3124,47 +3124,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,74 +3354,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2397</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>745460</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>742049</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>746893</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>706448</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>704531</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>704509</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>745460</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>741935</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>746891</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2079</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1448251</t>
+          <t>1448367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453744</t>
+          <t>1453742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,107 +4271,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4310</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>718</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3598</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3615</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488017</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>484425</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488017</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>485137</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>957410</t>
+          <t>957437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3254</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3275</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>184204</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>186849</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>184241</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356387</t>
+          <t>356922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,107 +4957,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4836</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1364</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4180</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>743480</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>740008</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>743480</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>740067</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1445035</t>
+          <t>1444289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
